--- a/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,6 +1097,624 @@
       <c r="AE6" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA\20260121182629_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>33052026.68631438</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4109564.654868746</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3355892.364856631</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3681227.266778203</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7790791.921646949</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3355892.364856631</v>
+      </c>
+      <c r="H7" t="n">
+        <v>402182.1750348969</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-2343206.521699083</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>23846366.74647499</v>
+      </c>
+      <c r="M7" t="n">
+        <v>33052026.68631438</v>
+      </c>
+      <c r="N7" t="n">
+        <v>23848.76246423453</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>23848.76246423453</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23846.36674647498</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.395717759555828</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.66700005531311</v>
+      </c>
+      <c r="W7" t="n">
+        <v>33052026.68631438</v>
+      </c>
+      <c r="X7" t="n">
+        <v>33052026.68631438</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260126111343_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10627369.87377799</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3972253.181138982</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3291402.626360988</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3606568.866798659</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7578822.047937641</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3291402.626360988</v>
+      </c>
+      <c r="H8" t="n">
+        <v>26394.60935553542</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-3702793.011684412</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3433543.601808235</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10627369.87377799</v>
+      </c>
+      <c r="N8" t="n">
+        <v>22892.66938047377</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>22892.66938047377</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>22890.29067872155</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.378701752214962</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.983000040054321</v>
+      </c>
+      <c r="W8" t="n">
+        <v>10627369.87377799</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10627369.87377799</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260126115512_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11462966.95251616</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3972253.181138982</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3291402.626360988</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3606568.866798659</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7578822.047937641</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3291402.626360988</v>
+      </c>
+      <c r="H9" t="n">
+        <v>47499.54362966031</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-2907822.931423931</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3453065.666011799</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11462966.95251616</v>
+      </c>
+      <c r="N9" t="n">
+        <v>23022.8164751642</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>23022.8164751642</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>23020.43777341199</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.378701752214962</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.355000019073486</v>
+      </c>
+      <c r="W9" t="n">
+        <v>11462966.95251616</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11462966.95251616</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260126115706_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12627654.65159985</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3969124.714083388</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3289933.309800418</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3604593.589549505</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7573718.303632894</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3289933.309800418</v>
+      </c>
+      <c r="H10" t="n">
+        <v>431892.7601097319</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-2486807.344853738</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3818917.622910543</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12627654.65159985</v>
+      </c>
+      <c r="N10" t="n">
+        <v>25461.82866380319</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>25461.82866380319</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>25459.45081940361</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.377844399577072</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.921999931335449</v>
+      </c>
+      <c r="W10" t="n">
+        <v>12627654.65159985</v>
+      </c>
+      <c r="X10" t="n">
+        <v>12627654.65159985</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260126115839_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14007276.24520995</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3966389.835302253</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3288648.84599982</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3602856.125685039</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7569245.960987292</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3288648.84599982</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1064978.797883823</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-2329333.185020416</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4413735.825359425</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14007276.24520995</v>
+      </c>
+      <c r="N11" t="n">
+        <v>29427.28257899428</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>29427.28257899428</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>29424.90550239616</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.377076598118085</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.570000171661377</v>
+      </c>
+      <c r="W11" t="n">
+        <v>14007276.24520995</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14007276.24520995</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260126120040_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15461960.01876915</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3964982.70983322</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3287987.975126734</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3601958.60192515</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7566941.31175837</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3287987.975126734</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1771550.48455435</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-2236648.445386198</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5072128.692715891</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15461960.01876915</v>
+      </c>
+      <c r="N12" t="n">
+        <v>33816.56796019931</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>33816.56796019931</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>33814.19128477262</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.376675426685899</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.244000196456909</v>
+      </c>
+      <c r="W12" t="n">
+        <v>15461960.01876915</v>
+      </c>
+      <c r="X12" t="n">
+        <v>15461960.01876915</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260126120253_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1715,6 +1715,521 @@
       <c r="AE12" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA\20260126120253_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10632383.76543888</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3972243.392728337</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3291398.029133782</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3606562.712590202</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7578806.105318539</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3291398.029133782</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12583.08977498814</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-3668293.21962927</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3417889.760840844</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10632383.76543888</v>
+      </c>
+      <c r="N13" t="n">
+        <v>22788.31043805332</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>22788.31043805332</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>22785.93173893896</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.378699114368705</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.144000053405762</v>
+      </c>
+      <c r="W13" t="n">
+        <v>10632383.76543888</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10632383.76543888</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260128180044_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11474265.66286202</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3972243.392728337</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3291398.029133782</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3606562.712590202</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7578806.105318539</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3291398.029133782</v>
+      </c>
+      <c r="H14" t="n">
+        <v>35945.8881588577</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-2865982.061968812</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3434097.702219653</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11474265.66286202</v>
+      </c>
+      <c r="N14" t="n">
+        <v>22896.36338057872</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>22896.36338057872</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>22893.98468146435</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.378699114368705</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.066999912261963</v>
+      </c>
+      <c r="W14" t="n">
+        <v>11474265.66286202</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11474265.66286202</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260128180302_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12767000.18372671</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3967581.975019723</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3289208.746615126</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3603614.638695342</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7571196.613715064</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3289208.746615126</v>
+      </c>
+      <c r="H15" t="n">
+        <v>547797.4516861945</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-2445827.708458884</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3804625.080169213</v>
+      </c>
+      <c r="M15" t="n">
+        <v>12767000.18372671</v>
+      </c>
+      <c r="N15" t="n">
+        <v>25366.54461437949</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>25366.54461437949</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>25364.16720112809</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.377413251389333</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.483999967575073</v>
+      </c>
+      <c r="W15" t="n">
+        <v>12767000.18372671</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12767000.18372671</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260128180523_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14357682.90743609</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3963478.075823446</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3287281.308369861</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3600996.257125421</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7564474.332948867</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3287281.308369861</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1391985.549224574</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-2290394.365227164</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4404336.082119948</v>
+      </c>
+      <c r="M16" t="n">
+        <v>14357682.90743609</v>
+      </c>
+      <c r="N16" t="n">
+        <v>29364.61678942527</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>29364.61678942527</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>29362.24054746632</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.376241958949042</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.573999881744385</v>
+      </c>
+      <c r="W16" t="n">
+        <v>14357682.90743609</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14357682.90743609</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260128180729_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16048599.52179025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3961021.98082126</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3286127.778223333</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3599418.553408733</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7560440.534229993</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3286127.778223333</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2338001.787695138</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-2205236.36615914</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5069265.787800925</v>
+      </c>
+      <c r="M17" t="n">
+        <v>16048599.52179025</v>
+      </c>
+      <c r="N17" t="n">
+        <v>33797.4807747201</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>33797.4807747201</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>33795.10525200616</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.375522713928874</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.28000020980835</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16048599.52179025</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16048599.52179025</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260128180958_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AE22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2230,6 +2230,521 @@
       <c r="AE17" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA\20260128180958_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10630997.08808911</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3971300.937581479</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3291398.029133782</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3606118.490387282</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7577419.427968761</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3291398.029133782</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12583.08977498814</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-3668293.219629269</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3417889.760840844</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10630997.08808911</v>
+      </c>
+      <c r="N18" t="n">
+        <v>22788.31043805332</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>22788.31043805332</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>22785.93173893896</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.378699114368705</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.209000110626221</v>
+      </c>
+      <c r="W18" t="n">
+        <v>10630997.08808911</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10630997.08808911</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260303113549_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>11472878.98551224</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3971300.937581479</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3291398.029133782</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3606118.490387282</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7577419.427968761</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3291398.029133782</v>
+      </c>
+      <c r="H19" t="n">
+        <v>35945.8881588577</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-2865982.061968812</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3434097.702219653</v>
+      </c>
+      <c r="M19" t="n">
+        <v>11472878.98551224</v>
+      </c>
+      <c r="N19" t="n">
+        <v>22896.36338057872</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>22896.36338057872</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>22893.98468146435</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.378699114368705</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.083999872207642</v>
+      </c>
+      <c r="W19" t="n">
+        <v>11472878.98551224</v>
+      </c>
+      <c r="X19" t="n">
+        <v>11472878.98551224</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260303113807_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>12765616.06738241</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3966641.260460024</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3289208.746615126</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3603171.236910735</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7569812.497370759</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3289208.746615126</v>
+      </c>
+      <c r="H20" t="n">
+        <v>547797.4516861945</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-2445827.708458884</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3804625.080169213</v>
+      </c>
+      <c r="M20" t="n">
+        <v>12765616.06738241</v>
+      </c>
+      <c r="N20" t="n">
+        <v>25366.54461437949</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>25366.54461437949</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>25364.16720112809</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.377413251389333</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.136000156402588</v>
+      </c>
+      <c r="W20" t="n">
+        <v>12765616.06738241</v>
+      </c>
+      <c r="X20" t="n">
+        <v>12765616.06738241</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260303114031_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>14356301.02713308</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3962577.690295069</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3287299.536407297</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3600578.433583683</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7563156.123878751</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3287299.536407297</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1391991.937409291</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-2290352.096638842</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4404205.526076586</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14356301.02713308</v>
+      </c>
+      <c r="N21" t="n">
+        <v>29363.74642705184</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>29363.74642705184</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>29361.3701738439</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.376253207936251</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.167999982833862</v>
+      </c>
+      <c r="W21" t="n">
+        <v>14356301.02713308</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14356301.02713308</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260303114241_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16047219.00953853</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3960083.715782794</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3286127.778223333</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3598976.306195484</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7559060.021978278</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3286127.778223333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2338001.787695138</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-2205236.36615914</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5069265.787800925</v>
+      </c>
+      <c r="M22" t="n">
+        <v>16047219.00953853</v>
+      </c>
+      <c r="N22" t="n">
+        <v>33797.4807747201</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>33797.4807747201</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>33795.10525200616</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.375522713928874</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.789000034332275</v>
+      </c>
+      <c r="W22" t="n">
+        <v>16047219.00953853</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16047219.00953853</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260303114521_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE29"/>
+  <dimension ref="A1:AE34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3466,6 +3466,521 @@
       <c r="AE29" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA\20260410155051_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4557475.58121415</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3968023.814578809</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8525499.395792959</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="H30" t="n">
+        <v>13919.8506283139</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-6700020.298860934</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3523967.731215771</v>
+      </c>
+      <c r="M30" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="N30" t="n">
+        <v>23495.48814467013</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>23495.48814467013</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>23493.11820810513</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.36993656499096</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.620999813079834</v>
+      </c>
+      <c r="W30" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="X30" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260416185629_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4557475.58121415</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3968023.814578809</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8525499.395792959</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="H31" t="n">
+        <v>20248.72024637644</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-5885594.056943642</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>3528358.384513303</v>
+      </c>
+      <c r="M31" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="N31" t="n">
+        <v>23524.75916665367</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>23524.75916665367</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>23522.38923008867</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.36993656499096</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.06600022315979</v>
+      </c>
+      <c r="W31" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="X31" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260416185840_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4557438.671832654</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3277746.352035474</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3968000.674175445</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8525439.3460081</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3277746.352035474</v>
+      </c>
+      <c r="H32" t="n">
+        <v>83162.95553301492</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-5122480.997625734</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3572123.150230736</v>
+      </c>
+      <c r="M32" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="N32" t="n">
+        <v>23816.52426160197</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>23816.52426160197</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>23814.15433487156</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.369926730408682</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.523999929428101</v>
+      </c>
+      <c r="W32" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="X32" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260416190056_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4547900.089093477</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3274151.466331838</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3961989.364587809</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8509889.453681286</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3274151.466331838</v>
+      </c>
+      <c r="H33" t="n">
+        <v>536705.0065737572</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-4662935.075997879</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3917905.448455236</v>
+      </c>
+      <c r="M33" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="N33" t="n">
+        <v>26121.73698830697</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>26121.73698830697</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>26119.36965636826</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.367331938715767</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7.085000038146973</v>
+      </c>
+      <c r="W33" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="X33" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260416190315_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4541223.293586039</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3271635.126392026</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3957744.482564553</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8498967.776150592</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3271635.126392026</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1236173.95706722</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-4394302.215786446</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4425719.911035368</v>
+      </c>
+      <c r="M34" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="N34" t="n">
+        <v>29507.16485901798</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>29507.16485901798</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>29504.79940690244</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.365452115534493</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.433000087738037</v>
+      </c>
+      <c r="W34" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="X34" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260416190525_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE34"/>
+  <dimension ref="A1:AE39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3981,6 +3981,521 @@
       <c r="AE34" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA\20260416190525_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4557475.58121415</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3968023.814578809</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8525499.395792959</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="H35" t="n">
+        <v>13919.8506283139</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-6700020.298860934</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3523967.731215771</v>
+      </c>
+      <c r="M35" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="N35" t="n">
+        <v>23495.48814467013</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>23495.48814467013</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>23493.11820810513</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.36993656499096</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6.016999959945679</v>
+      </c>
+      <c r="W35" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="X35" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260417161800_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4557475.58121415</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3968023.814578809</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8525499.395792959</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="H36" t="n">
+        <v>20248.72024637644</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-5885594.056943642</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3528358.384513303</v>
+      </c>
+      <c r="M36" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="N36" t="n">
+        <v>23524.75916665367</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>23524.75916665367</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23522.38923008867</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.36993656499096</v>
+      </c>
+      <c r="V36" t="n">
+        <v>5.706000089645386</v>
+      </c>
+      <c r="W36" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="X36" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260417162004_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4557438.671832654</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3277746.352035474</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3968000.674175445</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8525439.3460081</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3277746.352035474</v>
+      </c>
+      <c r="H37" t="n">
+        <v>83162.95553301492</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-5122480.997625734</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3572123.150230736</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="N37" t="n">
+        <v>23816.52426160197</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>23816.52426160197</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>23814.15433487156</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.369926730408682</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6.072000026702881</v>
+      </c>
+      <c r="W37" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="X37" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260417162212_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4547900.089093477</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3274151.466331838</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3961989.364587809</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8509889.453681286</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3274151.466331838</v>
+      </c>
+      <c r="H38" t="n">
+        <v>536705.0065737572</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-4662935.075997879</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3917905.448455236</v>
+      </c>
+      <c r="M38" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="N38" t="n">
+        <v>26121.73698830697</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>26121.73698830697</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>26119.36965636826</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.367331938715767</v>
+      </c>
+      <c r="V38" t="n">
+        <v>6.654999971389771</v>
+      </c>
+      <c r="W38" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="X38" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260417162421_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4541223.293586039</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3271635.126392026</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3957744.482564553</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8498967.776150592</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3271635.126392026</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1236173.95706722</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-4394302.215786446</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4425719.911035368</v>
+      </c>
+      <c r="M39" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="N39" t="n">
+        <v>29507.16485901798</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>29507.16485901798</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>29504.79940690244</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.365452115534493</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.035000085830688</v>
+      </c>
+      <c r="W39" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="X39" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260417162624_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE39"/>
+  <dimension ref="A1:AE44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4496,6 +4496,521 @@
       <c r="AE39" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA\20260417162624_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4557475.58121415</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3968023.814578809</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8525499.395792959</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13919.8506283139</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-6700020.298860934</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3523967.731215771</v>
+      </c>
+      <c r="M40" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="N40" t="n">
+        <v>23495.48814467013</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>23495.48814467013</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>23493.11820810513</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.36993656499096</v>
+      </c>
+      <c r="V40" t="n">
+        <v>6.335000038146973</v>
+      </c>
+      <c r="W40" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="X40" t="n">
+        <v>8641126.941159852</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260425225932_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4557475.58121415</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3968023.814578809</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8525499.395792959</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3277760.26238374</v>
+      </c>
+      <c r="H41" t="n">
+        <v>20248.72024637644</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-5885594.056943642</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3528358.384513303</v>
+      </c>
+      <c r="M41" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="N41" t="n">
+        <v>23524.75916665367</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>23524.75916665367</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>23522.38923008867</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.36993656499096</v>
+      </c>
+      <c r="V41" t="n">
+        <v>6.203999996185303</v>
+      </c>
+      <c r="W41" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="X41" t="n">
+        <v>9466272.705992736</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260425230146_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4557438.671832654</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3277746.352035474</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3968000.674175445</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8525439.3460081</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3277746.352035474</v>
+      </c>
+      <c r="H42" t="n">
+        <v>83162.95553301492</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-5122480.997625734</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3572123.150230736</v>
+      </c>
+      <c r="M42" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="N42" t="n">
+        <v>23816.52426160197</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>23816.52426160197</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>23814.15433487156</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.369926730408682</v>
+      </c>
+      <c r="V42" t="n">
+        <v>6.555000066757202</v>
+      </c>
+      <c r="W42" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10335990.80618159</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260425230405_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4547900.089093477</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3274151.466331838</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3961989.364587809</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8509889.453681286</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3274151.466331838</v>
+      </c>
+      <c r="H43" t="n">
+        <v>536705.0065737572</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-4662935.075997879</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3917905.448455236</v>
+      </c>
+      <c r="M43" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="N43" t="n">
+        <v>26121.73698830697</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>26121.73698830697</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>26119.36965636826</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.367331938715767</v>
+      </c>
+      <c r="V43" t="n">
+        <v>7.172999858856201</v>
+      </c>
+      <c r="W43" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="X43" t="n">
+        <v>11575716.29904424</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260425230628_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4541223.293586039</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3271635.126392026</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3957744.482564553</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8498967.776150592</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3271635.126392026</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1236173.95706722</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-4394302.215786446</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>4425719.911035368</v>
+      </c>
+      <c r="M44" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="N44" t="n">
+        <v>29507.16485901798</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>29507.16485901798</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>29504.79940690244</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2.365452115534493</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.581000089645386</v>
+      </c>
+      <c r="W44" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="X44" t="n">
+        <v>13038194.55485876</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260425230844_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>

--- a/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
+++ b/dataCaseStudy_WtE/raw_results/MEA/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE44"/>
+  <dimension ref="A1:AE49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5011,6 +5011,521 @@
       <c r="AE44" t="inlineStr">
         <is>
           <t>dataCaseStudy_WtE\raw_results\MEA\20260425230844_dh_ratio_1_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>10023577.38358968</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4538188.365383657</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3270491.327537979</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5336716.305057799</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9874904.670441456</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3270491.327537979</v>
+      </c>
+      <c r="H45" t="n">
+        <v>13887.14560098776</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-6723961.307925257</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3588255.54793451</v>
+      </c>
+      <c r="M45" t="n">
+        <v>10023577.38358968</v>
+      </c>
+      <c r="N45" t="n">
+        <v>23924.0682302529</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>23924.0682302529</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>23921.70365289673</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2.364577356171673</v>
+      </c>
+      <c r="V45" t="n">
+        <v>6.983999967575073</v>
+      </c>
+      <c r="W45" t="n">
+        <v>10023577.38358968</v>
+      </c>
+      <c r="X45" t="n">
+        <v>10023577.38358968</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>dh_ratio_0_costs</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260427135031_dh_ratio_0_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>10848723.14842256</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4538188.365383657</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3270491.327537979</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5336716.305057799</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>9874904.670441456</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3270491.327537979</v>
+      </c>
+      <c r="H46" t="n">
+        <v>20216.01521905029</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-5909535.066007968</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3592646.201232041</v>
+      </c>
+      <c r="M46" t="n">
+        <v>10848723.14842256</v>
+      </c>
+      <c r="N46" t="n">
+        <v>23953.33925223644</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>23953.33925223644</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>23950.97467488026</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2.364577356171673</v>
+      </c>
+      <c r="V46" t="n">
+        <v>6.523999929428101</v>
+      </c>
+      <c r="W46" t="n">
+        <v>10848723.14842256</v>
+      </c>
+      <c r="X46" t="n">
+        <v>10848723.14842256</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260427135249_dh_ratio_0.25_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>11718413.95541181</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4538081.084926945</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3270450.895852198</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5336629.270340586</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>9874710.355267532</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3270450.895852198</v>
+      </c>
+      <c r="H47" t="n">
+        <v>83097.37009011877</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-5146489.486020015</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3636644.820221976</v>
+      </c>
+      <c r="M47" t="n">
+        <v>11718413.95541181</v>
+      </c>
+      <c r="N47" t="n">
+        <v>24246.66334761276</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>24246.66334761276</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>24244.29880147984</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.364546132917662</v>
+      </c>
+      <c r="V47" t="n">
+        <v>7.069999933242798</v>
+      </c>
+      <c r="W47" t="n">
+        <v>11718413.95541181</v>
+      </c>
+      <c r="X47" t="n">
+        <v>11718413.95541181</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260427135510_dh_ratio_0.5_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>12956541.55214581</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4526763.393051574</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3266185.50236205</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5327351.922539422</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9854115.315590996</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3266185.50236205</v>
+      </c>
+      <c r="H48" t="n">
+        <v>534644.1752748359</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-4688817.351717876</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3990413.9106358</v>
+      </c>
+      <c r="M48" t="n">
+        <v>12956541.55214581</v>
+      </c>
+      <c r="N48" t="n">
+        <v>26605.12057466374</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>26605.12057466374</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>26602.75940423868</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.361170425057917</v>
+      </c>
+      <c r="V48" t="n">
+        <v>7.440999984741211</v>
+      </c>
+      <c r="W48" t="n">
+        <v>12956541.55214581</v>
+      </c>
+      <c r="X48" t="n">
+        <v>12956541.55214581</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260427135735_dh_ratio_0.75_costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>14417480.13243368</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4515924.552536473</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3262100.577601509</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5318281.133353937</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9834205.68589041</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3262100.577601509</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1231191.204887496</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-4424365.948631733</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4514348.612686002</v>
+      </c>
+      <c r="M49" t="n">
+        <v>14417480.13243368</v>
+      </c>
+      <c r="N49" t="n">
+        <v>30098.01519623173</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>30098.01519623173</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>30095.6574179067</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.357778325036549</v>
+      </c>
+      <c r="V49" t="n">
+        <v>7.21399998664856</v>
+      </c>
+      <c r="W49" t="n">
+        <v>14417480.13243368</v>
+      </c>
+      <c r="X49" t="n">
+        <v>14417480.13243368</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>dh_ratio_1_costs</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_WtE\raw_results\MEA\20260427135951_dh_ratio_1_costs</t>
         </is>
       </c>
     </row>
